--- a/Diarias/CustoKg.xlsx
+++ b/Diarias/CustoKg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F3E558-AA57-46F0-8B10-700A7263B75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB329EC-5B16-4C35-A385-BC50105190C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{202230F5-B999-493F-8126-8B87BE85ADD7}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +62,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1E293B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -121,6 +127,7 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,7 +563,9 @@
       <c r="E3" s="1">
         <v>4.5140548350636793</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1">
+        <v>4.6702628272672149</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -576,6 +585,8 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" s="1"/>
+      <c r="F7" s="5"/>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
@@ -595,26 +606,31 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>

--- a/Diarias/CustoKg.xlsx
+++ b/Diarias/CustoKg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Diarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB329EC-5B16-4C35-A385-BC50105190C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4355544-B761-40D1-BF11-9E1A1D0179D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{202230F5-B999-493F-8126-8B87BE85ADD7}"/>
   </bookViews>
@@ -552,21 +552,23 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>2.8419728136781184</v>
+        <v>2.6461576831247697</v>
       </c>
       <c r="C3" s="1">
-        <v>3.1693450343524985</v>
+        <v>2.9261391281684146</v>
       </c>
       <c r="D3" s="1">
-        <v>3.3854432983166687</v>
+        <v>3.4430057620262438</v>
       </c>
       <c r="E3" s="1">
-        <v>4.5140548350636793</v>
+        <v>4.1751156476852982</v>
       </c>
       <c r="F3" s="1">
-        <v>4.6702628272672149</v>
-      </c>
-      <c r="G3" s="1"/>
+        <v>17.83318862600391</v>
+      </c>
+      <c r="G3" s="1">
+        <v>36.023713088299353</v>
+      </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -576,6 +578,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C4" s="3"/>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
